--- a/data/focalizados.xlsx
+++ b/data/focalizados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\POI\POI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B791C3-B379-4A7A-9A15-A048BDF503AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA2F15B-A086-440A-934F-FBA52F6B9459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>RUC</t>
   </si>
@@ -59,19 +59,35 @@
   </si>
   <si>
     <t>AMA SACRED VALLEY EMPRESA INDIVIDUAL DE RESPONSABILIDAD LIMITADA</t>
+  </si>
+  <si>
+    <t>YUCRA HERRERA MAYRA CARLAY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Nova Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Nova Light"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,10 +112,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -406,19 +422,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -426,101 +442,112 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>10252209404</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>20607521493</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>20602527671</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>20494899940</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>20609862107</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>20609825171</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>10108083935</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>10431131752</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>10448929324</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10752532619</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
     </row>

--- a/data/focalizados.xlsx
+++ b/data/focalizados.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA2F15B-A086-440A-934F-FBA52F6B9459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA6B6D6-6598-494E-829B-C0256299B630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>RUC</t>
   </si>
   <si>
-    <t>RAZON_SOCIAL</t>
-  </si>
-  <si>
     <t>TIPO</t>
   </si>
   <si>
@@ -55,20 +55,38 @@
     <t>MIALAM S.R.L.</t>
   </si>
   <si>
-    <t>OFFICE LAND E.I.R.L.</t>
-  </si>
-  <si>
     <t>AMA SACRED VALLEY EMPRESA INDIVIDUAL DE RESPONSABILIDAD LIMITADA</t>
   </si>
   <si>
     <t>YUCRA HERRERA MAYRA CARLAY</t>
+  </si>
+  <si>
+    <t>RAZON SOCIAL</t>
+  </si>
+  <si>
+    <t>QUISPE AUCCACUSI TORIBIA</t>
+  </si>
+  <si>
+    <t>SALLO RAMOS MARLENY</t>
+  </si>
+  <si>
+    <t>HUALPA ZAPANA NANCY CARMEN</t>
+  </si>
+  <si>
+    <t>MODA TEXTIL TITIKAKA SOCIEDAD COMERCIAL DE RESPONSABILIDAD LIMITADA</t>
+  </si>
+  <si>
+    <t>BRG SOLUTIONS S.A.C.S.</t>
+  </si>
+  <si>
+    <t>MOSOQ ALPACA S.R.L.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,14 +95,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial Nova Light"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial Nova Light"/>
       <family val="2"/>
@@ -107,20 +130,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{044ED23D-A7E3-460F-A03E-9A682820AE00}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -422,133 +443,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>20611354160</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>10252209404</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>20607521493</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>20602527671</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>20494899940</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>20609862107</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>20602367704</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>10108083935</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>10431131752</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>20607521493</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>20602527671</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>20494899940</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>20609862107</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>20609825171</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10448929324</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>20610549587</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>10765621068</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>10752532619</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>10108083935</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>10431131752</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>10448929324</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10752532619</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>10239769018</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>10474747501</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
